--- a/artfynd/A 49665-2024 artfynd.xlsx
+++ b/artfynd/A 49665-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121222851</v>
       </c>
       <c r="B2" t="n">
-        <v>94737</v>
+        <v>94747</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49665-2024 artfynd.xlsx
+++ b/artfynd/A 49665-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121222851</v>
       </c>
       <c r="B2" t="n">
-        <v>94747</v>
+        <v>94759</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49665-2024 artfynd.xlsx
+++ b/artfynd/A 49665-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121222851</v>
       </c>
       <c r="B2" t="n">
-        <v>94759</v>
+        <v>94760</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49665-2024 artfynd.xlsx
+++ b/artfynd/A 49665-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121222851</v>
+        <v>121222832</v>
       </c>
       <c r="B2" t="n">
-        <v>94760</v>
+        <v>8435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508528</v>
+        <v>508529</v>
       </c>
       <c r="R2" t="n">
-        <v>6513378</v>
+        <v>6513368</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121222832</v>
+        <v>121222851</v>
       </c>
       <c r="B3" t="n">
-        <v>8432</v>
+        <v>94763</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508529</v>
+        <v>508528</v>
       </c>
       <c r="R3" t="n">
-        <v>6513368</v>
+        <v>6513378</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 49665-2024 artfynd.xlsx
+++ b/artfynd/A 49665-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121222832</v>
+        <v>121222851</v>
       </c>
       <c r="B2" t="n">
-        <v>8435</v>
+        <v>94763</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508529</v>
+        <v>508528</v>
       </c>
       <c r="R2" t="n">
-        <v>6513368</v>
+        <v>6513378</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121222851</v>
+        <v>121222832</v>
       </c>
       <c r="B3" t="n">
-        <v>94763</v>
+        <v>8435</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508528</v>
+        <v>508529</v>
       </c>
       <c r="R3" t="n">
-        <v>6513378</v>
+        <v>6513368</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 49665-2024 artfynd.xlsx
+++ b/artfynd/A 49665-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121222851</v>
       </c>
       <c r="B2" t="n">
-        <v>94763</v>
+        <v>94769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49665-2024 artfynd.xlsx
+++ b/artfynd/A 49665-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121222851</v>
       </c>
       <c r="B2" t="n">
-        <v>94769</v>
+        <v>94770</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49665-2024 artfynd.xlsx
+++ b/artfynd/A 49665-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121222851</v>
+        <v>121222832</v>
       </c>
       <c r="B2" t="n">
-        <v>94770</v>
+        <v>8435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508528</v>
+        <v>508529</v>
       </c>
       <c r="R2" t="n">
-        <v>6513378</v>
+        <v>6513368</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121222832</v>
+        <v>121222851</v>
       </c>
       <c r="B3" t="n">
-        <v>8435</v>
+        <v>94770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508529</v>
+        <v>508528</v>
       </c>
       <c r="R3" t="n">
-        <v>6513368</v>
+        <v>6513378</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
